--- a/output/planning_resultat.xlsx
+++ b/output/planning_resultat.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -521,13 +521,13 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -537,19 +537,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -571,19 +571,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -599,28 +599,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -636,13 +636,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -670,16 +670,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -729,19 +729,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -754,28 +754,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -797,13 +797,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -819,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -831,13 +831,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -847,28 +847,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -971,28 +971,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1023,7 +1023,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1070,22 +1070,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1095,16 +1095,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1113,7 +1113,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>3</v>
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1138,16 +1138,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1188,25 +1188,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>3</v>
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1237,10 +1237,10 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -1284,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1389,13 +1389,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1451,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>1</v>
@@ -1513,13 +1513,13 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1529,28 +1529,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1622,28 +1622,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1789,16 +1789,16 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1820,16 +1820,16 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -1842,25 +1842,25 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -1935,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -1972,19 +1972,19 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2065,19 +2065,19 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -2152,16 +2152,16 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2186,22 +2186,22 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2223,13 +2223,13 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>2</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2273,19 +2273,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -2319,13 +2319,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2335,28 +2335,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2431,7 +2431,7 @@
         <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2443,13 +2443,13 @@
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -2499,19 +2499,19 @@
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2527,19 +2527,19 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>2</v>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -2561,19 +2561,19 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -2586,16 +2586,16 @@
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>1</v>
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -2680,7 +2680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2737,105 +2737,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 42, Personne 60</t>
+          <t>Personne 20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 14, Personne 62</t>
+          <t>Personne 12, Personne 28, Personne 36</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 13, Personne 35</t>
+          <t>Personne 31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2849,260 +2849,229 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 09</t>
+          <t>Personne 58</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 67</t>
+          <t>Personne 21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 33, Personne 59</t>
+          <t>Personne 22, Personne 23, Personne 40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 08, Personne 50, Personne 67</t>
+          <t>Personne 52, Personne 62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 43, Personne 70</t>
+          <t>Personne 45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 10, Personne 16, Personne 18, Personne 62</t>
+          <t>Personne 37, Personne 50, Personne 64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 21, Personne 34</t>
+          <t>Personne 62</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 04, Personne 15, Personne 41</t>
+          <t>Personne 01, Personne 08</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 30, Personne 69</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -3119,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3181,7 +3150,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -3195,169 +3164,169 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 34</t>
+          <t>Personne 28, Personne 68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 15, Personne 63</t>
+          <t>Personne 25, Personne 46, Personne 53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 40, Personne 48</t>
+          <t>Personne 48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 46</t>
+          <t>Personne 54, Personne 70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 38, Personne 58</t>
+          <t>Personne 42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 01, Personne 30</t>
+          <t>Personne 15, Personne 21, Personne 39, Personne 42, Personne 57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3367,38 +3336,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 17, Personne 41, Personne 57</t>
+          <t>Personne 01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3412,55 +3381,55 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 18, Personne 35</t>
+          <t>Personne 02, Personne 44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 07, Personne 25, Personne 28, Personne 64</t>
+          <t>Personne 23, Personne 36, Personne 64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3474,14 +3443,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 11, Personne 52</t>
+          <t>Personne 07, Personne 25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3491,57 +3460,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 36, Personne 47, Personne 56</t>
+          <t>Personne 17, Personne 26</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 33, Personne 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -3558,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3615,64 +3553,64 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 23, Personne 65</t>
+          <t>Personne 68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 06</t>
+          <t>Personne 16, Personne 37, Personne 60, Personne 64</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3682,38 +3620,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 12, Personne 20</t>
+          <t>Personne 07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3727,14 +3665,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 53</t>
+          <t>Personne 54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3744,7 +3682,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3758,148 +3696,148 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 04, Personne 15</t>
+          <t>Personne 24, Personne 29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 26, Personne 61</t>
+          <t>Personne 29, Personne 32, Personne 33, Personne 47, Personne 65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 18, Personne 39, Personne 50</t>
+          <t>Personne 08, Personne 61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 19, Personne 33</t>
+          <t>Personne 18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 05, Personne 11, Personne 12, Personne 32</t>
+          <t>Personne 06, Personne 66</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3913,74 +3851,43 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 47, Personne 49</t>
+          <t>Personne 11, Personne 35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 29, Personne 44, Personne 55</t>
+          <t>Personne 09, Personne 59</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 31, Personne 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -3997,7 +3904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4054,136 +3961,136 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 34</t>
+          <t>Personne 30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 41, Personne 66</t>
+          <t>Personne 05, Personne 46, Personne 53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 05, Personne 70</t>
+          <t>Personne 07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 52</t>
+          <t>Personne 19, Personne 55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4197,45 +4104,45 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 31, Personne 61</t>
+          <t>Personne 19, Personne 31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 51, Personne 64</t>
+          <t>Personne 15, Personne 18, Personne 41, Personne 47, Personne 59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4245,38 +4152,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 20, Personne 47, Personne 65</t>
+          <t>Personne 08, Personne 61</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4290,76 +4197,76 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 37, Personne 59</t>
+          <t>Personne 12, Personne 48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 07, Personne 32, Personne 54, Personne 61</t>
+          <t>Personne 06, Personne 45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 51, Personne 53</t>
+          <t>Personne 04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4369,57 +4276,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 22, Personne 24, Personne 44</t>
+          <t>Personne 67, Personne 69</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 58, Personne 64</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -4436,7 +4312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4493,105 +4369,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 10, Personne 23</t>
+          <t>Personne 13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 17, Personne 22</t>
+          <t>Personne 03, Personne 63, Personne 69, Personne 70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 21, Personne 28</t>
+          <t>Personne 58</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -4605,76 +4481,76 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 44</t>
+          <t>Personne 52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 16, Personne 60</t>
+          <t>Personne 38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 09, Personne 68</t>
+          <t>Personne 14, Personne 22, Personne 43, Personne 55, Personne 57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4684,38 +4560,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 42, Personne 50, Personne 68</t>
+          <t>Personne 05, Personne 49</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4729,55 +4605,55 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 06, Personne 62</t>
+          <t>Personne 56, Personne 66</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 13, Personne 36, Personne 54, Personne 70</t>
+          <t>Personne 02, Personne 56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4791,24 +4667,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 09, Personne 37</t>
+          <t>Personne 04, Personne 67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4822,43 +4698,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 22, Personne 38, Personne 57</t>
+          <t>Personne 26, Personne 50, Personne 51</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 26, Personne 63</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -4875,7 +4720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4932,105 +4777,105 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 20, Personne 29</t>
+          <t>Personne 35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 19, Personne 59</t>
+          <t>Personne 03, Personne 34, Personne 63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 39, Personne 55</t>
+          <t>Personne 13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -5044,76 +4889,76 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 06</t>
+          <t>Personne 41</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 21, Personne 69</t>
+          <t>Personne 14</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 05</t>
+          <t>Personne 02, Personne 22, Personne 24, Personne 43, Personne 65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5123,38 +4968,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 08, Personne 12, Personne 23</t>
+          <t>Personne 20, Personne 33</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5168,86 +5013,86 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 48</t>
+          <t>Personne 03, Personne 49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 07, Personne 16, Personne 27, Personne 35</t>
+          <t>Personne 01, Personne 27, Personne 60</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 37, Personne 51</t>
+          <t>Personne 39</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5261,43 +5106,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 19, Personne 24, Personne 31</t>
+          <t>Personne 05, Personne 10, Personne 11</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 40, Personne 43</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>
@@ -5314,7 +5128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5376,100 +5190,100 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 29, Personne 45</t>
+          <t>Personne 13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 42, Personne 66</t>
+          <t>Personne 15, Personne 20, Personne 27, Personne 34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 55, Personne 60</t>
+          <t>Personne 38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -5483,179 +5297,179 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 46</t>
+          <t>Personne 70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 25, Personne 67</t>
+          <t>Personne 48</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 01, Personne 63</t>
+          <t>Personne 06, Personne 10, Personne 23, Personne 32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 10, Personne 14, Personne 17</t>
+          <t>Personne 40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 56, Personne 65</t>
+          <t>Personne 10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 08, Personne 13, Personne 27, Personne 32</t>
+          <t>Personne 17, Personne 44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -5669,24 +5483,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 49, Personne 52</t>
+          <t>Personne 16, Personne 30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5700,43 +5514,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 11, Personne 24, Personne 57</t>
+          <t>Personne 04, Personne 09, Personne 51</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Personne 40, Personne 43</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>(*) Personne affectée malgré une préférence de blocage (priorité 2)</t>
         </is>

--- a/output/planning_resultat.xlsx
+++ b/output/planning_resultat.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -502,11 +502,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Personne 01</t>
+          <t>Agathe Bouvet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -515,13 +515,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Personne 02</t>
+          <t>Alegria Lily Bulka</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Personne 03</t>
+          <t>Alexandra Bastian</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,32 +574,32 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Personne 04</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -620,35 +620,35 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Personne 05</t>
+          <t>Analou Ledru</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -657,7 +657,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Personne 06</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -667,50 +667,50 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Personne 07</t>
+          <t>Annouk Malric</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -719,26 +719,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Personne 08</t>
+          <t>Antonin Noël</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -750,14 +750,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Personne 09</t>
+          <t>Arsène Tessier</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -766,26 +766,26 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Personne 10</t>
+          <t>Arthur Uldry</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -794,25 +794,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Personne 11</t>
+          <t>Athénaé Marchand</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -831,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -843,26 +843,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Personne 12</t>
+          <t>Auxence Magerand</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Personne 13</t>
+          <t>Ava Baruch</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -884,35 +884,35 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Personne 14</t>
+          <t>Benoît Detrain</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -921,26 +921,26 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Personne 15</t>
+          <t>Corentin Meige</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -949,7 +949,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -967,38 +967,38 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Personne 16</t>
+          <t>Emma De Filippo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Personne 17</t>
+          <t>Enzo Maître</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Personne 18</t>
+          <t>Eugénie Prouvost</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1054,29 +1054,29 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Personne 19</t>
+          <t>Iris Rakotonandrasana</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1085,20 +1085,20 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Personne 20</t>
+          <t>Jamilah Bürgisser</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1110,57 +1110,57 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Personne 21</t>
+          <t>Jolan Ruscio</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Personne 22</t>
+          <t>Jonas Wuilloud</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1172,10 +1172,10 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
@@ -1184,11 +1184,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Personne 23</t>
+          <t>Jules Pirolley</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1197,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>3</v>
@@ -1215,17 +1215,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Personne 24</t>
+          <t>Julie Chavaillaz</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1237,23 +1237,23 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Personne 25</t>
+          <t>Kristel Oeschger</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>2</v>
@@ -1277,26 +1277,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Personne 26</t>
+          <t>Léa Baltzinger</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1308,14 +1308,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Personne 27</t>
+          <t>Léa Chambaz</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1327,32 +1327,32 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Personne 28</t>
+          <t>Lina-Rosa Ledru</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1370,20 +1370,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Personne 29</t>
+          <t>Lisa Jaquet</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1395,13 +1395,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Personne 30</t>
+          <t>Lisa Magnin</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1426,13 +1426,13 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Personne 31</t>
+          <t>Louis Cardis</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1457,13 +1457,13 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Personne 32</t>
+          <t>Louis Post</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1473,13 +1473,13 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1494,7 +1494,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Personne 33</t>
+          <t>Louise Blanchard</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1510,10 +1510,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1525,7 +1525,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Personne 34</t>
+          <t>Lucas Chastroux</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
@@ -1556,7 +1556,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Personne 35</t>
+          <t>Lucie Meyer</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1569,32 +1569,32 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Personne 36</t>
+          <t>Maëlan Ménétrey</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1618,60 +1618,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Personne 37</t>
+          <t>Maëlle Chambaz</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Personne 38</t>
+          <t>Marius Felix</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>2</v>
@@ -1680,14 +1680,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Personne 39</t>
+          <t>Marot Ledru</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1711,14 +1711,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Personne 40</t>
+          <t>Mathis Cuinet</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -1742,7 +1742,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Personne 41</t>
+          <t>Matteo Gavin</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1752,10 +1752,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1773,14 +1773,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Personne 42</t>
+          <t>Maxime Debray</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1804,11 +1804,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Personne 43</t>
+          <t>Maya Corbelli</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -1817,35 +1817,35 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Personne 44</t>
+          <t>Mickaël Pasche</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Personne 45</t>
+          <t>Morgana Fargues</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1879,25 +1879,25 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Personne 46</t>
+          <t>Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1910,25 +1910,25 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Personne 47</t>
+          <t>Nathalia Koux</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -1959,26 +1959,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Personne 48</t>
+          <t>Noah Cherpillod</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -1990,7 +1990,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Personne 49</t>
+          <t>Patrick Chambaz</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -2000,13 +2000,13 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -2021,14 +2021,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Personne 50</t>
+          <t>Rama Assaoui</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2052,17 +2052,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Personne 51</t>
+          <t>Raphaël Lacroze</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2074,32 +2074,32 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Personne 52</t>
+          <t>Raphaëlle Neidhart</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -2108,13 +2108,13 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Personne 53</t>
+          <t>Roxanne Lanni</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2124,10 +2124,10 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -2136,23 +2136,23 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Personne 54</t>
+          <t>Sébastien Schiesser</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2176,11 +2176,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Personne 55</t>
+          <t>Simon Lambelet</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
@@ -2192,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2201,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Personne 56</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2226,19 +2226,19 @@
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Personne 57</t>
+          <t>Thibault Clerici</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2248,13 +2248,13 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2263,29 +2263,29 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Personne 58</t>
+          <t>Titouan Ménétrey</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Personne 59</t>
+          <t>Tristan Clerici</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2319,50 +2319,50 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Personne 60</t>
+          <t>Yann Bally</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Personne 61</t>
+          <t>Ysatis Ménétrey</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2388,285 +2388,6 @@
       </c>
       <c r="I62" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Personne 62</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Personne 63</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Personne 64</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Personne 65</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Personne 66</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Personne 67</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Personne 68</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Personne 69</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Personne 70</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2732,19 +2453,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
@@ -2756,24 +2477,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 20</t>
+          <t>Kristel Oeschger</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2787,55 +2508,55 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 12, Personne 28, Personne 36</t>
+          <t>Marot Ledru, Maxime Debray, Maya Corbelli</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 31</t>
+          <t>Analou Ledru, Léa Chambaz</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2849,76 +2570,76 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 58</t>
+          <t>Louis Cardis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 21</t>
+          <t>Emma De Filippo, Simon Lambelet</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 22, Personne 23, Personne 40</t>
+          <t>Morgana Fargues</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2928,40 +2649,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 52, Personne 62</t>
+          <t>Arthur Uldry, Rama Assaoui, Yann Bally</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
@@ -2973,55 +2694,55 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 45</t>
+          <t>Simon Lambelet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 37, Personne 50, Personne 64</t>
+          <t>Alice L'Horset</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -3035,38 +2756,38 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 62</t>
+          <t>Léa Chambaz</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 01, Personne 08</t>
+          <t>Corentin Meige, Lina-Rosa Ledru, Noah Cherpillod</t>
         </is>
       </c>
     </row>
@@ -3140,79 +2861,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 28, Personne 68</t>
+          <t>Iris Rakotonandrasana</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 25, Personne 46, Personne 53</t>
+          <t>Alegria Lily Bulka, Benoît Detrain, Jonas Wuilloud, Lisa Jaquet, Thibault Clerici</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -3226,24 +2947,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 48</t>
+          <t>Jamilah Bürgisser</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -3257,138 +2978,138 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 54, Personne 70</t>
+          <t>Enzo Maître, Mathis Cuinet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 42</t>
+          <t>Arsène Tessier, Raphaël Lacroze</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 15, Personne 21, Personne 39, Personne 42, Personne 57</t>
+          <t>Antonin Noël, Marius Felix</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 01</t>
+          <t>Léa Chambaz, Roxanne Lanni, Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 44</t>
+          <t>Agathe Bouvet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3398,33 +3119,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 23, Personne 36, Personne 64</t>
+          <t>Rama Assaoui, Raphaëlle Neidhart</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3443,19 +3164,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 07, Personne 25</t>
+          <t>Analou Ledru, Corentin Meige</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3464,17 +3185,17 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 17, Personne 26</t>
+          <t>Jules Pirolley, Julie Chavaillaz, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3269,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3562,24 +3283,24 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 68</t>
+          <t>Thibault Clerici, Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3589,100 +3310,100 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 16, Personne 37, Personne 60, Personne 64</t>
+          <t>Ava Baruch, Eugénie Prouvost, Lisa Jaquet, Matteo Gavin, Roxanne Lanni</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 07</t>
+          <t>Raphaëlle Neidhart, Sébastien Schiesser</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 54</t>
+          <t>Arsène Tessier, Louis Cardis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -3696,55 +3417,55 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 24, Personne 29</t>
+          <t>Annouk Malric, Auxence Magerand</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 29, Personne 32, Personne 33, Personne 47, Personne 65</t>
+          <t>Louise Blanchard</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -3758,14 +3479,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 08, Personne 61</t>
+          <t>Mickaël Pasche, Patrick Chambaz</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3775,7 +3496,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -3789,76 +3510,76 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 18</t>
+          <t>Lisa Magnin</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 06, Personne 66</t>
+          <t>Iris Rakotonandrasana</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 11, Personne 35</t>
+          <t>Raphaël Lacroze</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3868,21 +3589,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 09, Personne 59</t>
+          <t>Alexandra Bastian, Jolan Ruscio, Léa Baltzinger, Lucie Meyer</t>
         </is>
       </c>
     </row>
@@ -3956,38 +3677,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 30</t>
+          <t>Eugénie Prouvost, Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3997,100 +3718,100 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 05, Personne 46, Personne 53</t>
+          <t>Ava Baruch, Lucas Chastroux, Marius Felix, Maya Corbelli, Thibault Clerici</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 07</t>
+          <t>Lisa Magnin, Titouan Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 19, Personne 55</t>
+          <t>Louis Cardis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4104,55 +3825,55 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 19, Personne 31</t>
+          <t>Enzo Maître, Jules Pirolley</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 15, Personne 18, Personne 41, Personne 47, Personne 59</t>
+          <t>Alexandra Bastian, Simon Lambelet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4166,45 +3887,45 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 08, Personne 61</t>
+          <t>Arthur Uldry, Eugénie Prouvost</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 12, Personne 48</t>
+          <t>Nathalia Koux</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4214,7 +3935,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -4228,24 +3949,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 06, Personne 45</t>
+          <t>Lisa Jaquet, Raphaëlle Neidhart</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4259,38 +3980,38 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 04</t>
+          <t>Jolan Ruscio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 67, Personne 69</t>
+          <t>Agathe Bouvet, Lina-Rosa Ledru, Lucie Meyer</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4085,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4374,7 +4095,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -4388,19 +4109,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 13</t>
+          <t>Marot Ledru</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4409,158 +4130,158 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 63, Personne 69, Personne 70</t>
+          <t>Alegria Lily Bulka, Antonin Noël, Jonas Wuilloud, Maxime Debray, Maya Corbelli</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 58</t>
+          <t>Agathe Bouvet, Theo Cyprien</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 52</t>
+          <t>Annouk Malric, Emma De Filippo</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 38</t>
+          <t>Arsène Tessier, Louis Post, Raphaël Lacroze</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 14, Personne 22, Personne 43, Personne 55, Personne 57</t>
+          <t>Iris Rakotonandrasana, Yann Bally</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4574,45 +4295,45 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 05, Personne 49</t>
+          <t>Louise Blanchard, Morgana Fargues</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 56, Personne 66</t>
+          <t>Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4622,59 +4343,59 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 56</t>
+          <t>Ysatis Ménétrey</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 04, Personne 67</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4684,21 +4405,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 26, Personne 50, Personne 51</t>
+          <t>Lucie Meyer, Maëlle Chambaz, Morgane Scyboz (Lambelet), Yann Bally</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4796,19 +4517,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 35</t>
+          <t>Jolan Ruscio</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4817,65 +4538,65 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 34, Personne 63</t>
+          <t>Alegria Lily Bulka, Julie Chavaillaz, Lucas Chastroux, Noah Cherpillod, Tristan Clerici</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 13</t>
+          <t>Antonin Noël, Benoît Detrain</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -4889,138 +4610,138 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 41</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 14</t>
+          <t>Auxence Magerand, Léa Baltzinger, Matteo Gavin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 02, Personne 22, Personne 24, Personne 43, Personne 65</t>
+          <t>Maëlan Ménétrey, Mickaël Pasche</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 20, Personne 33</t>
+          <t>Jules Pirolley, Morgana Fargues, Patrick Chambaz</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 03, Personne 49</t>
+          <t>Anna Mallet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5030,33 +4751,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 01, Personne 27, Personne 60</t>
+          <t>Sébastien Schiesser</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5075,14 +4796,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 39</t>
+          <t>Theo Cyprien</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5092,7 +4813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -5106,7 +4827,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 05, Personne 10, Personne 11</t>
+          <t>Emma De Filippo, Maëlan Ménétrey, Maëlle Chambaz</t>
         </is>
       </c>
     </row>
@@ -5180,17 +4901,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -5204,24 +4925,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Personne 13</t>
+          <t>Corentin Meige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Accueil</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -5235,24 +4956,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Personne 15, Personne 20, Personne 27, Personne 34</t>
+          <t>Jonas Wuilloud, Julie Chavaillaz, Kristel Oeschger, Mickaël Pasche</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Vestiaire</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -5266,107 +4987,107 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Personne 38</t>
+          <t>Benoît Detrain</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Billetterie</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Personne 70</t>
+          <t>Nathalia Koux, Noah Cherpillod</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Personne 48</t>
+          <t>Analou Ledru, Annouk Malric, Louis Post</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bar</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Personne 06, Personne 10, Personne 23, Personne 32</t>
+          <t>Roxanne Lanni</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vestiaire</t>
+          <t>Sécurité</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5380,34 +5101,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personne 40</t>
+          <t>Enzo Maître, Mathis Cuinet</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -5421,14 +5142,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personne 10</t>
+          <t>Athénaé Marchand</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sécurité</t>
+          <t>Billetterie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5438,59 +5159,59 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Personne 17, Personne 44</t>
+          <t>Maëlle Chambaz</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personne 16, Personne 30</t>
+          <t>Jamilah Bürgisser</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Accueil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5500,21 +5221,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Personne 04, Personne 09, Personne 51</t>
+          <t>Alice L'Horset, Athénaé Marchand, Lisa Magnin, Morgane Scyboz (Lambelet)</t>
         </is>
       </c>
     </row>
